--- a/samples/X-Webtechnologien/WT-BoxmodelleVergleichen/GUI-Konzept.xlsx
+++ b/samples/X-Webtechnologien/WT-BoxmodelleVergleichen/GUI-Konzept.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hscoburgde-my.sharepoint.com/personal/ale8155s_hs-coburg_de/Documents/Masterprojekt/2-Modellierung/Lernmodulkonfigurationen/X-Webtechnologien/WT-BoxmodelleVergleichen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{CFBEDF05-9CAF-4806-963C-1DF1F041B20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1066506-FDA3-46F7-B273-61709099BA6D}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{CFBEDF05-9CAF-4806-963C-1DF1F041B20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D15CC111-94F6-4783-BF41-E0072150DCFE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DB19C3B3-13CE-4CBB-98B3-625F51AA7CBF}"/>
   </bookViews>
@@ -306,15 +306,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -323,31 +339,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -682,301 +680,306 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF64E799-A56E-49F1-8DF6-708395F6088C}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="3" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="9"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="20"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="3" t="s">
+      <c r="D2" s="18"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="11"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="3" t="s">
+      <c r="H2" s="12"/>
+      <c r="I2" s="4"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="14"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="H3" s="12"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="20"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="15" t="s">
+      <c r="D4" s="15"/>
+      <c r="E4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="15" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="16"/>
-      <c r="K4" s="15" t="s">
+      <c r="J4" s="15"/>
+      <c r="K4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="15" t="s">
+      <c r="L4" s="15"/>
+      <c r="M4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="16"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="3" t="s">
+      <c r="N4" s="13"/>
+      <c r="O4" s="20"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="9"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="3" t="s">
+      <c r="H5" s="12"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="20"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="20" t="s">
+      <c r="H6" s="12"/>
+      <c r="I6" s="4"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="14"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="H7" s="19"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="20"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="3" t="s">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="13"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="1" t="s">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="1" t="s">
+      <c r="J9" s="12"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="M9" s="12"/>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="1" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="1" t="s">
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="M10" s="12"/>
+      <c r="N10" s="13"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="1" t="s">
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="1" t="s">
+      <c r="J11" s="12"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="M11" s="12"/>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="1" t="s">
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="1" t="s">
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="M12" s="12"/>
+      <c r="N12" s="13"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="1" t="s">
+      <c r="E13" s="12"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="1" t="s">
+      <c r="J13" s="12"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="2"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="I11:K11"/>
@@ -989,24 +992,14 @@
     <mergeCell ref="L9:N9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="L10:N10"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="L12:N12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
